--- a/Tests/g17_setup1_with_1ed_sim_outputs.xlsx
+++ b/Tests/g17_setup1_with_1ed_sim_outputs.xlsx
@@ -1,42 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5440292_ad_unsw_edu_au/Documents/MyPhD-Workspace/Codes/LoRaMeshSimulator-V3/Tests/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2C352103DB4738CFEB3B98154B5DCE3A87473E73" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C22EC9C8-7641-4E50-8849-517D12F34C7E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -55,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -357,10 +407,211 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I1" t="n">
+        <v>3098.856206443471</v>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K1" t="n">
+        <v>3068.145626459736</v>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M1" t="n">
+        <v>3130.423959321342</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2898.552358993019</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2841.942546507344</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>2948.509186495095</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3092.159048875361</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2806.137142042164</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>4001.014171928167</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3161.447240878717</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2441.128696590662</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3721.377990454435</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Tests/g17_setup1_with_1ed_sim_outputs.xlsx
+++ b/Tests/g17_setup1_with_1ed_sim_outputs.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -426,10 +426,10 @@
         <v>3</v>
       </c>
       <c r="D1" t="n">
-        <v>3600000</v>
+        <v>10000</v>
       </c>
       <c r="E1" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="F1" t="inlineStr">
         <is>
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>3098.856206443471</v>
+        <v>3160.296349178773</v>
       </c>
       <c r="J1" t="inlineStr">
         <is>
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="K1" t="n">
-        <v>3068.145626459736</v>
+        <v>59.02441188320518</v>
       </c>
       <c r="L1" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="M1" t="n">
-        <v>3130.423959321342</v>
+        <v>27250.68447063304</v>
       </c>
     </row>
     <row r="2">
@@ -475,10 +475,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3600000</v>
+        <v>20000</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2898.552358993019</v>
+        <v>3316.064824346746</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2841.942546507344</v>
+        <v>56.87332554720342</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2948.509186495095</v>
+        <v>29970.00729409792</v>
       </c>
     </row>
     <row r="3">
@@ -524,10 +524,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3600000</v>
+        <v>30000</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3092.159048875361</v>
+        <v>3428.92615750902</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2806.137142042164</v>
+        <v>60.19994493946433</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>4001.014171928167</v>
+        <v>24808.61110525485</v>
       </c>
     </row>
     <row r="4">
@@ -573,10 +573,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3600000</v>
+        <v>40000</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3161.447240878717</v>
+        <v>3182.366199608689</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2441.128696590662</v>
+        <v>57.41541673615575</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -608,7 +608,105 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3721.377990454435</v>
+        <v>20238.89758048207</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3040.721233797079</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>63.5209624543786</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>20794.12405123189</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3135.924618098682</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>52.54934802278876</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>20101.71023960784</v>
       </c>
     </row>
   </sheetData>
